--- a/materials.xlsx
+++ b/materials.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="匠魂材料" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="宋体"/>
       <family val="2"/>
@@ -39,8 +40,17 @@
       <sz val="9"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +60,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -91,6 +111,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -456,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="21.08984375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -474,6 +504,12 @@
     <col width="27.54296875" bestFit="1" customWidth="1" min="15" max="15"/>
     <col width="17.90625" bestFit="1" customWidth="1" min="16" max="16"/>
     <col width="41.6328125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="19"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="23"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="33" customHeight="1">
@@ -562,6 +598,36 @@
           <t>防御特性描述</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>远程特性ID</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>远程特性名</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>远程特性描述</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>近战部件</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>弓部件</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>护甲部件</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -641,6 +707,36 @@
           <t>加2个防御槽位</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>galtc2:sprb</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>SPRB</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>每级加2个升级槽位，1个能力槽位</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
@@ -717,7 +813,37 @@
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>延长受到攻击后的无敌帧</t>
+          <t>延长受到攻击后的无敌帧（原版 20 刻 → 30 刻），挡掉连续多段伤害。</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>galtc2:eightstrike_ranged</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>八段刺·乱射</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>一次射击射出 8 支箭，每支都是完整箭矢伤害，且只消耗 1 支弹药。</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>可做</t>
         </is>
       </c>
     </row>
@@ -784,11 +910,53 @@
           <t>净化负面效果</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
-    </row>
-    <row r="5">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:kagome</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>代偿</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>净化负面效果</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>galtc2:kagome</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>代偿</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>净化负面效果</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>aosora</t>
@@ -838,22 +1006,64 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>galtc2:aosora</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>苍彼</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>手持苍彼武器近战命中时，把目标向上抛起约 64 格；箭矢命中时把目标向上抛起约 32 格，之后自然下坠。</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>galtc2:celestial</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>翱翔</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>创造飞行</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>穿在身上时获得飞行能力（护甲侧特性）。</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>galtc2:aosora</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>苍彼</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>手持苍彼武器近战命中时，把目标向上抛起约 64 格；箭矢命中时把目标向上抛起约 32 格，之后自然下坠。</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -909,24 +1119,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>galtc2:aia</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>AI护甲</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>收到50次伤害后，提高一点盔甲和盔甲韧性</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
-      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="8" t="n"/>
+      <c r="S6" s="8" t="n"/>
+      <c r="T6" s="8" t="n"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -982,24 +1210,42 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>galtc2:aid</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>AI抵抗</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>受到伤害后抵御同类伤害30s</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
-      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="8" t="n"/>
+      <c r="S7" s="8" t="n"/>
+      <c r="T7" s="8" t="n"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1061,7 +1307,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>额外造成目标最大血量15%的伤害</t>
+          <t>额外造成目标最大生命 15%/级的伤害；远程额外伤害不超过该箭伤害的 3 倍。</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1077,6 +1323,36 @@
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>免疫低于自身最大生命值的伤害</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>galtc2:narcissus</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>水仙</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>额外造成目标最大生命 15%/级的伤害；远程额外伤害不超过该箭伤害的 3 倍。</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>可做</t>
         </is>
       </c>
     </row>
@@ -1158,8 +1434,38 @@
           <t>获得幸运值×幸运值 的护甲值</t>
         </is>
       </c>
-    </row>
-    <row r="10">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>galtc2:valuation</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>对赌</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>受幸运值影响：小概率反噬自身，反噬倍率最高 1.5 倍；大概率对敌方造成 1～99 倍伤害。</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>steinsgate</t>
@@ -1207,24 +1513,42 @@
           <t>下界合金</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>galtc2:steinsgate</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>石头门</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>假死后会血量和2s无敌，有60s cd</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>死亡时假死一次：保留 20% 生命并获得 3 秒无敌，冷却 120 秒（护甲侧特性）。</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="n"/>
+      <c r="S10" s="8" t="n"/>
+      <c r="T10" s="8" t="n"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1304,8 +1628,26 @@
           <t>防御数值超过 50 时翻 3 倍</t>
         </is>
       </c>
-    </row>
-    <row r="12">
+      <c r="R11" s="8" t="n"/>
+      <c r="S11" s="8" t="n"/>
+      <c r="T11" s="8" t="n"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>nighttimesheep</t>
@@ -1383,8 +1725,38 @@
           <t>防御数值低于 18 时补足到 18</t>
         </is>
       </c>
-    </row>
-    <row r="13">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>galtc2:nighttimesheep</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>夜羊</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>低于18的攻击数值有额外加成</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>oumunnbyou</t>
@@ -1447,9 +1819,51 @@
           <t>樱花印记叠到5层后樱纹病爆发</t>
         </is>
       </c>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:oumnnbyou_armor</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>樱花印记</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>受到攻击时，把樱花印记叠给攻击者（最多 5 层）。</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>galtc2:oumunnbyou</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>樱纹病</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>樱花印记叠到5层后樱纹病爆发</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1529,6 +1943,36 @@
           <t>来自蜘蛛类的伤害减免 50%</t>
         </is>
       </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>galtc2:kisaragikurenai</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>月影魅像</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>对非蜘蛛生物造成额外伤害</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1580,16 +2024,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>galtc2:tagetes
-galtc2:lavare
-galtc2:rosmarinus</t>
+          <t>galtc2:tagetes,galtc2:lavare,galtc2:rosmarinus</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>万寿菊
-薰衣草
-迷迭香</t>
+          <t>万寿菊,薰衣草,迷迭香</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1614,6 +2054,36 @@
           <t>按已损失生命提升护甲，并对高生命或高护甲的攻击者最多减伤 30%</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>galtc2:rosmarinus</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>迷迭香</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3秒控制</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1675,14 +2145,56 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>杀敌对生物后要击杀友好生物</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n"/>
-    </row>
-    <row r="17">
+          <t>杀敌对生物后要击杀友好生物；箭矢命中时扣 1 点血。</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:muramasa</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>村正</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>杀敌对生物后要击杀友好生物；箭矢命中时扣 1 点血。</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>galtc2:muramasa</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>村正</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>杀敌对生物后要击杀友好生物；箭矢命中时扣 1 点血。</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>shochou</t>
@@ -1760,6 +2272,36 @@
           <t>按物品栏中的钱财数量提升防御（每件 +0.25，上限 +20）</t>
         </is>
       </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>galtc2:shochou</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>财迷</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>攻击有概率获得钱财，冷却2秒</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1839,8 +2381,26 @@
           <t>受伤回血，回复量随词条等级提升</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
+      <c r="R18" s="8" t="n"/>
+      <c r="S18" s="8" t="n"/>
+      <c r="T18" s="8" t="n"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>nishiki_asumi</t>
@@ -1918,6 +2478,36 @@
           <t>装备时不会掉饱食度</t>
         </is>
       </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>galtc2:vtb</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Vtb</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>攻击时附加50%最大生命值的额外伤害</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1997,8 +2587,38 @@
           <t>获取额外护甲值和盔甲韧性，大的是护甲值，小的是韧性</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>galtc2:qien</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>奇恩</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>根据当前时间附加伤害，取分钟和小时中最大的值</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>rewrite</t>
@@ -2058,14 +2678,44 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>获得攻击对象的护甲值和血量，持续到目标死亡或60秒</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
+          <t>命中时复写目标的护甲与生命上限加到自己身上，可叠加；每份持续 60 秒，或到该目标死亡为止。</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:rewrite_armor</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>改写</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>受到攻击时，复写攻击者的护甲、坚韧与生命上限加到自己身上，持续 5 秒；对方不会被修改，生命上限每 5 秒最多复写一次。</t>
+        </is>
+      </c>
+      <c r="R21" s="8" t="n"/>
+      <c r="S21" s="8" t="n"/>
+      <c r="T21" s="8" t="n"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>badwoman</t>
@@ -2143,8 +2793,26 @@
           <t>提供额外护盾，受伤时优先消耗，每秒恢复1点</t>
         </is>
       </c>
-    </row>
-    <row r="23" ht="56" customHeight="1">
+      <c r="R22" s="8" t="n"/>
+      <c r="S22" s="8" t="n"/>
+      <c r="T22" s="8" t="n"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
           <t>galaxy_railroad</t>
@@ -2194,41 +2862,65 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>galtc2:wonderful
-galtc2:camus_melee
-galtc2:starry_travel</t>
+          <t>galtc2:starry_travel,galtc2:camus_melee</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>素晴日
-晴空下的加缪
-星空列车与白的旅行</t>
+          <t>星空列车与白的旅行,晴空下的加缪</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>超过72格高度摔落时伤害翻倍
-天气晴朗时，近战命中给目标下禁疗诅咒。
-离出生点越远伤害越高，每5区块+1伤害</t>
+          <t>离出生点越远伤害越高，每5区块+1伤害
+天气晴朗时，近战命中给目标下禁疗诅咒。</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>galtc2:starry_travel_armor
-galtc2:camus_armor</t>
+          <t>galtc2:starry_travel_armor,galtc2:camus_armor</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>星空列车与白的旅行
-晴空下的加缪的防御特性</t>
+          <t>星空列车与白的旅行,晴空下的加缪的防御特性</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>离出生点越远护甲越高，每5区块+1护甲
+          <t>离出生点越远，护甲与坚韧越高（任何实体穿戴都生效）。
 天气晴朗时，受到伤害给攻击者下禁疗诅咒。</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>galtc2:starry_travel,galtc2:camus_melee</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>星空列车与白的旅行,晴空下的加缪</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>离出生点越远伤害越高，每5区块+1伤害
+天气晴朗时，近战命中给目标下禁疗诅咒。</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>可做</t>
         </is>
       </c>
     </row>
@@ -2310,6 +3002,36 @@
           <t>受到攻击时播放丛雨丸音效</t>
         </is>
       </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>galtc2:ciallo</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>丛雨丸~</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>攻击时播放丛雨丸音效</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="70" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -2361,14 +3083,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>galtc2:kisaki_likes
-galtc2:kisaki_hates</t>
+          <t>galtc2:kisaki_likes,galtc2:kisaki_hates</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>可最喜欢你
-可最讨厌你</t>
+          <t>可最喜欢你,可最讨厌你</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -2392,6 +3112,36 @@
           <t>每穿着一个游戏日获得4%全属性减伤（上限80%）。代价：绑定诅咒；火焰伤害翻倍且无视减伤；着火后无法熄灭；因火焰伤害死亡时减伤清零并强制卸下</t>
         </is>
       </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>galtc2:kisaki_likes</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>可最喜欢你</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>攻击近期伤害过你的生物，返还其造成伤害的30%/级</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -2471,6 +3221,36 @@
           <t>受到伤害后，召唤一只触手反击攻击者。</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>galtc2:saya_melee</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>触袭</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>近战命中后，在目标附近召唤一只触手协助攻击。</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -2535,9 +3315,51 @@
           <t>近战或箭矢命中时，在目标处召唤疫病虫群；存在时间 1 级 10 秒、之后每级 +5 秒，攻击力也随等级提升。</t>
         </is>
       </c>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
-      <c r="Q27" s="2" t="n"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:qingfeng</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>清枫</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>近战或箭矢命中时，在目标处召唤疫病虫群；存在时间 1 级 10 秒、之后每级 +5 秒，攻击力也随等级提升。</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>galtc2:qingfeng</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>清枫</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>近战或箭矢命中时，在目标处召唤疫病虫群；存在时间 1 级 10 秒、之后每级 +5 秒，攻击力也随等级提升。</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -2617,6 +3439,36 @@
           <t>受到伤害时，给攻击者挂上随机负面效果。</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>galtc2:morgana_melee</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>咒袭</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>近战命中或箭矢命中时，给目标挂上随机负面效果。</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="70" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -2696,6 +3548,36 @@
           <t>每级提供 5% 抗击退；单次受到 6 点以上的伤害时减免 30%。</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>galtc2:echo_slam</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>回响震击</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>右键蓄力后松手，砸向前方地面：前方 5 格 / 120 度内造成「面板伤害 × 蓄力秒数 × 等级」的伤害，附带 5 秒裂甲与击退；蓄力上限 9 秒（蓄满自动落锤），冷却 5 秒、与回响钟锤共用。</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -2775,6 +3657,36 @@
           <t>来自复魂尸和沉降类生物的伤害减免 25%</t>
         </is>
       </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>galtc2:ancient_second_rounder</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>复魂尸杀手</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>近战攻击对复魂尸及沉降类生物造成额外伤害（类似亡灵杀手）。</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2839,9 +3751,51 @@
           <t>近战或箭矢命中时，在目标处降下不洁血雨。</t>
         </is>
       </c>
-      <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="n"/>
-      <c r="Q31" s="2" t="n"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:euthanasia</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>腐姬</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>近战或箭矢命中时，在目标处降下不洁血雨。</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>galtc2:euthanasia</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>腐姬</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>近战或箭矢命中时，在目标处降下不洁血雨。</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2921,6 +3875,36 @@
           <t>每件护甲降低火系承伤。</t>
         </is>
       </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>galtc2:serpon_alloy_melee</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>龙炎</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>提升自身造成的火系伤害。</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="84" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -2972,14 +3956,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>galtc2:moon_cleave
-galtc2:kin_bond</t>
+          <t>galtc2:moon_cleave,galtc2:kin_bond</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>斩月双刀
-亲人的羁绊</t>
+          <t>斩月双刀,亲人的羁绊</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -2990,14 +3972,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>galtc2:holy_warrior
-galtc2:kin_bond</t>
+          <t>galtc2:holy_warrior,galtc2:kin_bond</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>圣战士
-亲人的羁绊</t>
+          <t>圣战士,亲人的羁绊</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -3006,6 +3986,36 @@
 近战命中或被攻击时基础 20% 概率获得随机正面效果（速度/力量/抗性提升/生命恢复）持续8秒；概率受自身幸运值影响。</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>galtc2:moon_cleave</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>斩月双刀</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>近战命中前基础 20% 概率造成双倍伤害；概率受自身幸运值影响（套用迎战的幸运公式）。</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -3085,6 +4095,36 @@
           <t>穿戴后，每件护甲降低16%的冰冻类伤害（加算叠加）。</t>
         </is>
       </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>galtc2:giant_monster_hair_melee</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>霜噬</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>近战命中后，附加等量的冰冻类伤害。</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -3134,22 +4174,14 @@
           <t>下界合金</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>galtc2:meror_resistance</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>莫厄增伤</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 每级提升12%的莫厄伤害</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="inlineStr">
         <is>
           <t>莫厄减伤</t>
@@ -3158,6 +4190,36 @@
       <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>非莫厄来源的伤害每级减免12%(满级4级)。穿戴多件带此特性的护甲时等级叠加，4件1级等效4级。莫厄伤害不减伤。</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>galtc2:meror_bolt</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>莫厄箭</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>箭矢命中时追加莫厄伤害：箭矢基础伤害的50%/100%(等级1/2)，每支箭只结算一次；该伤害会被 J村 认定为莫厄伤害，不受莫厄减伤影响。</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>可做</t>
         </is>
       </c>
     </row>
@@ -3239,8 +4301,38 @@
           <t>单次伤害超过最大生命值50%时，该次伤害减半（多件护甲只结算一次）。</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>galtc2:mossy_spike</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>藓牙牙刺</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>近战命中后追加 +2 穿甲伤害（无视护甲）。</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="42" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
           <t>mountain_realm</t>
@@ -3303,9 +4395,51 @@
           <t>任意一件护甲即可生效：震慑直视目标、近战击飞小型生物、疾跑时虚弱附近生物、并清除自身缓慢与虚弱。</t>
         </is>
       </c>
-      <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n"/>
-      <c r="Q37" s="2" t="n"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:mountain_realm</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>镇山</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>任意一件护甲即可生效：震慑直视目标、近战击飞小型生物、疾跑时虚弱附近生物、并清除自身缓慢与虚弱。</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>galtc2:mountain_realm</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>镇山</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>任意一件护甲即可生效：震慑直视目标、近战击飞小型生物、疾跑时虚弱附近生物、并清除自身缓慢与虚弱。</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -3367,7 +4501,7 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>方块触及距离 +2；近战对发光的生物造成 +50% 伤害。</t>
+          <t>方块触及距离 +2；近战与箭矢命中都生效，对发光的生物额外造成 +50%/级的伤害。</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -3382,7 +4516,37 @@
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>方块触及距离 +2；近战对发光的生物造成 +50% 伤害。</t>
+          <t>方块触及距离 +2；近战与箭矢命中都生效，对发光的生物额外造成 +50%/级的伤害。</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>galtc2:soul_eater</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>魂喰</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>方块触及距离 +2；近战与箭矢命中都生效，对发光的生物额外造成 +50%/级的伤害。</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>可做</t>
         </is>
       </c>
     </row>
@@ -3449,9 +4613,51 @@
           <t>佩戴或手持时获得水下呼吸。</t>
         </is>
       </c>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
-      <c r="Q39" s="2" t="n"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:qoaiku_metal</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>鲙酷之力</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>佩戴或手持时获得水下呼吸。</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>galtc2:qoaiku_metal</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>鲙酷之力</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>佩戴或手持时获得水下呼吸。</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="56" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -3501,34 +4707,56 @@
           <t>下界合金</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>galtc2:meror_standard</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>莫厄制式</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>每级增加30%的莫厄伤害。</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="n"/>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>莫厄制式</t>
-        </is>
-      </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>夜视/真视(水中水下呼吸)、力量、潜行隐身、疾跑加速与跳跃提升；减免8点窒息与4点伤害(魔法命中减速攻击者)、免疫摔落；额外减伤30%。</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+          <t>任意一件护甲即可生效：夜视/真视(水中水下呼吸)、力量、潜行隐身、疾跑加速与跳跃提升；减免8点窒息与4点伤害(魔法命中减速攻击者)、免疫摔落；额外减伤30%。</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>galtc2:meror_bolt</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>莫厄箭</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>箭矢命中时追加莫厄伤害：箭矢基础伤害的50%/100%(等级1/2)，每支箭只结算一次；该伤害会被 J村 认定为莫厄伤害，不受莫厄减伤影响。</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
           <t>scaly_bear_scale</t>
@@ -3606,6 +4834,36 @@
           <t>来自中立生物的伤害减少 20%</t>
         </is>
       </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>galtc2:scaly_bear_scale</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>鳞熊之力</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>对友好生物造成的伤害 +20%（每级）。</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3685,6 +4943,24 @@
           <t>每件护甲降低火系承伤。</t>
         </is>
       </c>
+      <c r="R42" s="8" t="n"/>
+      <c r="S42" s="8" t="n"/>
+      <c r="T42" s="8" t="n"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3764,6 +5040,24 @@
           <t>受到伤害时呼唤暗乱反击。</t>
         </is>
       </c>
+      <c r="R43" s="8" t="n"/>
+      <c r="S43" s="8" t="n"/>
+      <c r="T43" s="8" t="n"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="28" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -3843,6 +5137,36 @@
           <t>对亡灵与暗夜巫妖造成的伤害提高 25%，受到来自它们的伤害降低 25%。</t>
         </is>
       </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>galtc2:soul_heart</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>魂人</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>对亡灵与暗夜巫妖造成的伤害提高 25%，受到来自它们的伤害降低 25%。</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="70" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -3895,14 +5219,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>galtc2:tianjin_zui
-galtc2:tianjin_zui_no_spawn</t>
+          <t>galtc2:tianjin_zui,galtc2:tianjin_zui_no_spawn</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>天津罪·其一
-天津罪·其二</t>
+          <t>天津罪·其一,天津罪·其二</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -3911,9 +5233,53 @@
 手持或穿戴时，领域内无法生成新的生物。</t>
         </is>
       </c>
-      <c r="O45" s="2" t="n"/>
-      <c r="P45" s="2" t="n"/>
-      <c r="Q45" s="2" t="n"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>galtc2:tianjin_zui,galtc2:tianjin_zui_no_spawn</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>天津罪·其一,天津罪·其二</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>手持或穿戴时展开禁飞领域，使周围 10 格内的生物无法飞行。领域半径随等级提高。
+手持或穿戴时，领域内无法生成新的生物。</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>galtc2:tianjin_zui,galtc2:tianjin_zui_no_spawn</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>天津罪·其一,天津罪·其二</t>
+        </is>
+      </c>
+      <c r="T45" s="6" t="inlineStr">
+        <is>
+          <t>手持或穿戴时展开禁飞领域，使周围 10 格内的生物无法飞行。领域半径随等级提高。
+手持或穿戴时，领域内无法生成新的生物。</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -3975,7 +5341,7 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>附近每只村民提升5%近战伤害（16格内，最多16只）。</t>
+          <t>附近每只村民提升 5% 近战伤害（16 格内，最多 16 只）；箭矢命中时额外造成周围村民数量（上限 16）点伤害/级。</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
@@ -3991,6 +5357,36 @@
       <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>附近每只村民降低5%受到的伤害（16格内，最多16只，最多减伤80%）。</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>galtc2:villager_metal_melee</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>乡勇</t>
+        </is>
+      </c>
+      <c r="T46" s="7" t="inlineStr">
+        <is>
+          <t>附近每只村民提升 5% 近战伤害（16 格内，最多 16 只）；箭矢命中时额外造成周围村民数量（上限 16）点伤害/级。</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>可做</t>
         </is>
       </c>
     </row>
@@ -4060,6 +5456,404 @@
           <t>被攻击时 25% 概率在攻击者身旁召唤蔷薇怨灵：它会跟着你、一直追着你的敌人打，直到敌人倒下或15秒后消散（冷却10秒）。</t>
         </is>
       </c>
+      <c r="R47" s="8" t="n"/>
+      <c r="S47" s="8" t="n"/>
+      <c r="T47" s="8" t="n"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>shaday</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>天镜龙魂</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Aether Dragon Soul</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>深蓝与琥珀的阴影金属（天境阴影套同色）</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>#2a4a82</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I48" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J48" t="n">
+        <v>7</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>下界合金</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>galtc2:shaday</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>丸子与银河龙</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>命中时附带天境龙的爪击粒子特效；对非天境生物造成 50% 额外伤害（天境本体 / 基石生物 / 天境龙的生物不吃额外伤害）。</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>galtc2:shaday_armor</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>龙背上的骑兵</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>骑乘天境龙时，受到的伤害先减免 50%，剩下的由坐骑承担；四件护甲只由第一件结算。</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>galtc2:shaday_ranged</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>龙姬混～日子</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>弹射物命中后，在命中点周围 5×5 范围内依次降下 5 根龙刺（大号滴水石锥）：落地前有收缩预警环，顶起时造成范围伤害并挑飞。</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>jiuhu</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>酒狐</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Jiu Hu</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>酒狐干活的时候会悄悄攒下这些锭……她大概是想给你做点什么。你对她越好，她攒得越快——好感度每涨一点，她都会立刻再多收五个进背包。不过她也只是个姑娘，连着干一整天就会累趴，得让她歇满一天才缓得过来。</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>#d08a4e</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>4</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1314</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J49" t="n">
+        <v>6</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>钻石</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>galtc2:love_grows</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>日久生情</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>按酒狐的好感度为工具补基础面板（耐久 / 攻击伤害 / 挖掘速度）：0~63 点 +1，64~127 点 +2，128~191 点 +3，192 点以上 +4；词条等级会乘算。多只酒狐时按好感度最高的那只算；女仆被收进魂符时也会读取魂符里保存的好感度。</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>galtc2:one_heart</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>同心</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>玩家穿戴时：酒狐承受伤害的 80% 转由玩家承受。酒狐穿戴时：为酒狐提供抗性提升 II 与生命恢复 III。</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>galtc2:true_love</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>挚爱</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>箭矢命中后，使目标 5 秒内优先索敌「除了玩家与酒狐以外」的生物；对 boss 不生效。</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>可做</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>字段</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>远程特性ID/名/描述</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>该材料做弓/弩部件（bow_limb / bow_grip）时实际生效的词条；空 = 当前没有远程词条（已标黄，可直接填）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>近战部件</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>能否做 head / handle / binding；"—" 表示该材料的这些部件 stats 未注册。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>弓部件</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>能否做 limb / grip（弓肢 / 弓握把）；只有"有远程词条"的材料才保留。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>护甲部件</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>能否做 plating_* / maille（盔甲与盾）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>判定口径</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>部件有效词条 = 显式 perStat[部件] → perStat[组] → default；head/handle/binding→melee_harvest，limb/grip/bowstring→ranged，plating/maille→armor。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>gating 规则</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>有效词条为空的部件已从 stats 删除（与石头门只留护甲 plating 同口径）；2026-10-27 F-026 清理 32 个材料 / 73 个部件键，同日 F-029 又为 27 个材料恢复 limb+grip 并挂上远程词条、izumi_hiyori 反向删除 limb+grip。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>当前远程词条</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>39 条 / 38 个材料（部件级条目 40 个）：ancient_second_rounder(ancient_second_rounder)、aosora(aosora)、camus_melee(galaxy_railroad)、ciallo(ciallo)、echo_slam(resonant_plate)、eightstrike_ranged(zeroone)、euthanasia(euthanasia)、giant_monster_hair_melee(giant_monster_hair)、kagome(kagome)、kisaki_likes(tsukiyashiro_kisaki)、kisaragikurenai(kisaragikurenai)、meror_bolt(meror/refine_meror)、moon_cleave(fortunes_favor)、morgana_melee(morgana)、mossy_spike(mossy_tooth)、mountain_realm(mountain_realm)、muramasa(muramasa)、narcissus(narcissus)、nighttimesheep(nighttimesheep)、oumunnbyou(oumunnbyou)、qien(qienidian)、qingfeng(qingfeng)、qoaiku_metal(qoaiku_metal)、rosmarinus(blacklily)、saya_melee(saya)、scaly_bear_scale(scaly_bear_scale)、serpon_alloy_melee(fire_apostle)、shaday_ranged(shaday)、shochou(shochou)、soul_eater(phantoplasm)、soul_heart(soul_heart)、sprb(sprb)、starry_travel(galaxy_railroad)、tianjin_zui(tianjin_zui)、tianjin_zui_no_spawn(tianjin_zui)、true_love(jiuhu)、valuation(ca)、villager_metal_melee(villager_metal)、vtb(nishiki_asumi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>grip 注意</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.20.1 的 grip 只用于 bow_grip（弓/弩），近战工具不用 grip；删 grip = 取消弓握把，不影响近战。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>如何加远程词条</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>① 在 traits/&lt;材料&gt;.json 的 perStat 里加 "tconstruct:ranged": [{"name":"galtc2:xxx","level":1}]；② 在 stats/&lt;材料&gt;.json 把 limb / grip 补回来（数值照抄旧值或参考同档材料）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表内缺失材料</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>脚本自动按 stats / definition / lang / 材质渲染 json 补行（本次补录 jiuhu / 酒狐）；可重复运行，不会重复追加。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>重跑行为</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>第 1–11 列只在补行时写入；12–23 列每次按当前 JSON 重算：词条为空则整组清空，描述取 lang 的 modifier.*.description（多条用换行分隔）；改描述请改 lang 后重跑。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
